--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484873_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484873_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7601</v>
+        <v>2.1171</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9912</v>
+        <v>5.401</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.2311</v>
+        <v>-3.284</v>
       </c>
       <c r="G2" t="n">
         <v>2.6677</v>
@@ -610,13 +610,13 @@
         <v>1.6983</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7829</v>
+        <v>-1.4259</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.749</v>
+        <v>-0.3391</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0339</v>
+        <v>-1.0868</v>
       </c>
       <c r="V2" t="n">
         <v>1.4415</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.7428</v>
+        <v>-3.2279</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0183</v>
+        <v>3.4539</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.7611</v>
+        <v>-6.6818</v>
       </c>
       <c r="G3" t="n">
         <v>-4.3648</v>
@@ -688,13 +688,13 @@
         <v>1.6983</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8195</v>
+        <v>-1.3046</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5501</v>
+        <v>-0.0143</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3696</v>
+        <v>-1.2902</v>
       </c>
       <c r="V3" t="n">
         <v>2.0641</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SERNEGUET GARVI</t>
+          <t>M. GONZALEZ ESPOSITO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.8354</v>
+        <v>-3.7573</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5092</v>
+        <v>-0.4994</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.3447</v>
+        <v>-3.2579</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.1543</v>
+        <v>-2.6769</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5613</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.593</v>
+        <v>-1.8528</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0684</v>
+        <v>1.0661</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8868</v>
+        <v>1.4689</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1816</v>
+        <v>-0.4028</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.2227</v>
+        <v>-3.7431</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.4481</v>
+        <v>-2.293</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7746</v>
+        <v>-1.4501</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.7175</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.0384</v>
+        <v>-1.1322</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3209</v>
+        <v>1.1322</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2163</v>
+        <v>-0.9558</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2533</v>
+        <v>-0.4333</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4696</v>
+        <v>-0.5225</v>
       </c>
       <c r="V4" t="n">
-        <v>4.2527</v>
+        <v>-0.1245</v>
       </c>
       <c r="W4" t="n">
-        <v>6.226</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.9733</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GONZALEZ ESPOSITO</t>
+          <t>A. SERNEGUET GARVI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.4174</v>
+        <v>-4.5006</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9479</v>
+        <v>2.3732</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.4696</v>
+        <v>-6.8737</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6769</v>
+        <v>-3.1543</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-1.5613</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8528</v>
+        <v>-1.593</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0661</v>
+        <v>2.0684</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4689</v>
+        <v>1.8868</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4028</v>
+        <v>0.1816</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.7431</v>
+        <v>-5.2227</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.293</v>
+        <v>-3.4481</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4501</v>
+        <v>-1.7746</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-4.7175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1322</v>
+        <v>-6.0384</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1322</v>
+        <v>1.3209</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.616</v>
+        <v>-0.8814</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8818</v>
+        <v>0.1172</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7342</v>
+        <v>-0.9986</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1245</v>
+        <v>4.2527</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>6.226</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1245</v>
+        <v>-1.9733</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. DURAN OLMOS</t>
+          <t>C. SEVERA LENCINA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-7.1652</v>
+        <v>-6.7839</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7421</v>
+        <v>-2.0211</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.4231</v>
+        <v>-4.7628</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.2248</v>
+        <v>-3.5474</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.0302</v>
+        <v>-3.0584</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1946</v>
+        <v>-0.489</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3866</v>
+        <v>0.457</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6292</v>
+        <v>0.2754</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7574</v>
+        <v>0.1816</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.6114</v>
+        <v>-4.0044</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.6594</v>
+        <v>-3.3338</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.952</v>
+        <v>-0.6706</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1322</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2644</v>
+        <v>-2.0757</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4385</v>
+        <v>-1.4252</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1357</v>
+        <v>-0.4024</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.5742</v>
+        <v>-1.0228</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3697</v>
+        <v>-1.2452</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3697</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. SEVERA LENCINA</t>
+          <t>I. DURAN OLMOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-7.5126</v>
+        <v>-7.1728</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7233</v>
+        <v>-1.0143</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.7893</v>
+        <v>-6.1585</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.5474</v>
+        <v>-3.2248</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.0584</v>
+        <v>-3.0302</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.489</v>
+        <v>-0.1946</v>
       </c>
       <c r="J7" t="n">
-        <v>0.457</v>
+        <v>1.3866</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2754</v>
+        <v>0.6292</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1816</v>
+        <v>0.7574</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.0044</v>
+        <v>-4.6114</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.3338</v>
+        <v>-3.6594</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6706</v>
+        <v>-0.952</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5661</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0757</v>
+        <v>-2.2644</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5096</v>
+        <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.1539</v>
+        <v>-1.4461</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1046</v>
+        <v>-0.1365</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0492</v>
+        <v>-1.3096</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2452</v>
+        <v>-1.3697</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2452</v>
+        <v>-1.3697</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-23.9133</v>
+        <v>-23.3254</v>
       </c>
       <c r="E8" t="n">
-        <v>7.105399999999998</v>
+        <v>7.693300000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-31.0189</v>
+        <v>-31.0187</v>
       </c>
       <c r="G8" t="n">
         <v>-14.3005</v>
@@ -1069,7 +1069,7 @@
         <v>-6.924300000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-6.6045</v>
+        <v>-6.604500000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>-15.096</v>
@@ -1078,13 +1078,13 @@
         <v>8.4915</v>
       </c>
       <c r="S8" t="n">
-        <v>-8.027099999999999</v>
+        <v>-7.439</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.7963</v>
+        <v>-1.2084</v>
       </c>
       <c r="U8" t="n">
-        <v>-6.2307</v>
+        <v>-6.230499999999999</v>
       </c>
       <c r="V8" t="n">
         <v>5.0189</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>7.6846</v>
+        <v>7.1338</v>
       </c>
       <c r="E9" t="n">
-        <v>8.061400000000001</v>
+        <v>7.6716</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3767</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>6.7486</v>
@@ -1156,13 +1156,13 @@
         <v>1.1322</v>
       </c>
       <c r="S9" t="n">
-        <v>2.0116</v>
+        <v>1.4608</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2556</v>
+        <v>0.8658</v>
       </c>
       <c r="U9" t="n">
-        <v>0.756</v>
+        <v>0.595</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3208</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8386</v>
+        <v>6.0272</v>
       </c>
       <c r="E10" t="n">
-        <v>6.6793</v>
+        <v>6.7584</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8407</v>
+        <v>-0.7312</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8266</v>
+        <v>4.0117</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8979</v>
+        <v>2.8189</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0714</v>
+        <v>1.1928</v>
       </c>
       <c r="J10" t="n">
-        <v>3.365</v>
+        <v>6.1026</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1593</v>
+        <v>3.5029</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2057</v>
+        <v>2.5997</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5384</v>
+        <v>-2.0909</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2614</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.277</v>
+        <v>-1.4069</v>
       </c>
       <c r="P10" t="n">
-        <v>1.887</v>
+        <v>0.1887</v>
       </c>
       <c r="Q10" t="n">
+        <v>-0.9435</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.1322</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.2975</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.887</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.125</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.0692</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.0559</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.2452</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-1.2452</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.4463</v>
+        <v>5.6085</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4661</v>
+        <v>3.7883</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0198</v>
+        <v>1.8202</v>
       </c>
       <c r="G11" t="n">
-        <v>4.0117</v>
+        <v>2.5074</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8189</v>
+        <v>1.105</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1928</v>
+        <v>1.4024</v>
       </c>
       <c r="J11" t="n">
-        <v>6.1026</v>
+        <v>2.6448</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5029</v>
+        <v>1.8704</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5997</v>
+        <v>0.7744</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0909</v>
+        <v>-0.1374</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.7654</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4069</v>
+        <v>0.628</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1887</v>
+        <v>1.5096</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9689</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0052</v>
+        <v>0.5209</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0611</v>
+        <v>0.448</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3018</v>
+        <v>0.6226</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3018</v>
+        <v>0.6226</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.9212</v>
+        <v>4.6694</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9941</v>
+        <v>5.5101</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0729</v>
+        <v>-0.8407</v>
       </c>
       <c r="G12" t="n">
-        <v>1.451</v>
+        <v>1.8266</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0055</v>
+        <v>2.8979</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4455</v>
+        <v>-1.0714</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6007</v>
+        <v>3.365</v>
       </c>
       <c r="K12" t="n">
-        <v>1.242</v>
+        <v>3.1593</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3588</v>
+        <v>0.2057</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1497</v>
+        <v>-1.5384</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2365</v>
+        <v>-0.2614</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0868</v>
+        <v>-1.277</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6983</v>
+        <v>1.887</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6983</v>
+        <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7152</v>
+        <v>0.9558</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8463</v>
+        <v>0.8999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8689</v>
+        <v>0.0559</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9434</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.547</v>
+        <v>1.2452</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4904</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6355</v>
+        <v>4.0705</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1063</v>
+        <v>3.1259</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5292</v>
+        <v>0.9446</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5074</v>
+        <v>3.1777</v>
       </c>
       <c r="H13" t="n">
-        <v>1.105</v>
+        <v>3.3096</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4024</v>
+        <v>-0.1319</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6448</v>
+        <v>2.7669</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8704</v>
+        <v>2.7258</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7744</v>
+        <v>0.0411</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1374</v>
+        <v>0.4108</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7654</v>
+        <v>0.5838</v>
       </c>
       <c r="O13" t="n">
-        <v>0.628</v>
+        <v>-0.173</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5096</v>
+        <v>0.7548</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5096</v>
+        <v>0.7548</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0041</v>
+        <v>-0.1638</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1611</v>
+        <v>0.0572</v>
       </c>
       <c r="U13" t="n">
-        <v>0.157</v>
+        <v>-0.221</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6226</v>
+        <v>0.3018</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6226</v>
+        <v>0.3018</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7012</v>
+        <v>3.983</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8336</v>
+        <v>5.2146</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8676</v>
+        <v>-1.2316</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1777</v>
+        <v>1.451</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3096</v>
+        <v>0.0055</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1319</v>
+        <v>1.4455</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7669</v>
+        <v>2.6007</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7258</v>
+        <v>1.242</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0411</v>
+        <v>1.3588</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4108</v>
+        <v>-1.1497</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5838</v>
+        <v>-1.2365</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.173</v>
+        <v>0.0868</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7548</v>
+        <v>1.6983</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7548</v>
+        <v>1.6983</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5331</v>
+        <v>1.777</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2352</v>
+        <v>1.0669</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.298</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3018</v>
+        <v>-0.9434</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3018</v>
+        <v>1.547</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1703</v>
+        <v>0.2278</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8429</v>
+        <v>1.1352</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0132</v>
+        <v>-0.9074</v>
       </c>
       <c r="G15" t="n">
         <v>1.1807</v>
@@ -1624,13 +1624,13 @@
         <v>1.5096</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.2738</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3527</v>
+        <v>-0.0604</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3192</v>
+        <v>-0.2134</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2452</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6519</v>
+        <v>-0.5641</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8204</v>
+        <v>1.723</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4723</v>
+        <v>-2.2871</v>
       </c>
       <c r="G16" t="n">
         <v>-0.229</v>
@@ -1702,13 +1702,13 @@
         <v>0.7548</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9546</v>
+        <v>2.0423</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6671</v>
+        <v>1.5696</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2875</v>
+        <v>0.4727</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2452</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6551</v>
+        <v>-0.7958</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0526</v>
+        <v>-1.9551</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3975</v>
+        <v>1.1594</v>
       </c>
       <c r="G17" t="n">
         <v>-1.9349</v>
@@ -1780,13 +1780,13 @@
         <v>1.6983</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5249</v>
+        <v>0.3843</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1611</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6861</v>
+        <v>0.448</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2367</v>
+        <v>-1.4248</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6412</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5955</v>
+        <v>-0.4656</v>
       </c>
       <c r="G18" t="n">
         <v>-2.0698</v>
@@ -1858,13 +1858,13 @@
         <v>1.6983</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9217</v>
+        <v>-0.1098</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5291</v>
+        <v>0.153</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3926</v>
+        <v>-0.2627</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.5999</v>
+        <v>-4.3726</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0914</v>
+        <v>-0.994</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.5085</v>
+        <v>-3.3786</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3694</v>
@@ -1936,13 +1936,13 @@
         <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1176</v>
+        <v>0.1098</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1735</v>
+        <v>-0.076</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0559</v>
+        <v>0.1858</v>
       </c>
       <c r="V19" t="n">
         <v>-2.4904</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>23.9135</v>
+        <v>24.5629</v>
       </c>
       <c r="E20" t="n">
-        <v>31.0189</v>
+        <v>31.0188</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.1053</v>
+        <v>-6.4558</v>
       </c>
       <c r="G20" t="n">
         <v>14.3006</v>
@@ -2002,7 +2002,7 @@
         <v>-6.190200000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-6.6006</v>
+        <v>-6.600599999999999</v>
       </c>
       <c r="P20" t="n">
         <v>6.604500000000001</v>
@@ -2014,13 +2014,13 @@
         <v>15.096</v>
       </c>
       <c r="S20" t="n">
-        <v>8.027000000000001</v>
+        <v>8.676500000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>6.2307</v>
+        <v>6.230700000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7964</v>
+        <v>2.446</v>
       </c>
       <c r="V20" t="n">
         <v>-5.018800000000001</v>
